--- a/data/Cercis.xlsx
+++ b/data/Cercis.xlsx
@@ -1,12 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miriamhafkin/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF49511E-DFFA-9342-8179-878D8074AFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="24960" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1564,33 +1586,39 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1598,58 +1626,53 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1839,20 +1862,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S157"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="28.25"/>
+    <col min="3" max="3" width="28.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1911,9 +1937,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>196267.0</v>
+        <v>196267</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
@@ -1926,13 +1952,13 @@
         <v>21</v>
       </c>
       <c r="F2" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G2" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H2" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>22</v>
@@ -1947,30 +1973,32 @@
         <v>24</v>
       </c>
       <c r="M2" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P2" s="4"/>
-      <c r="Q2" s="6" t="str">
-        <f t="shared" ref="Q2:Q157" si="1">(M2/(M2+ N2 +O2))</f>
+      <c r="Q2" s="6" t="e">
+        <f t="shared" ref="Q2:Q157" si="0">(M2/(M2+ N2 +O2))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R2" s="6" t="str">
-        <f t="shared" ref="R2:R157" si="2">(N2/(M2+ N2 +O2))</f>
+      <c r="R2" s="6" t="e">
+        <f t="shared" ref="R2:R157" si="1">(N2/(M2+ N2 +O2))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S2" s="6" t="str">
-        <f t="shared" ref="S2:S157" si="3">(O2/(M2+ N2 +O2))</f>
+      <c r="S2" s="6" t="e">
+        <f t="shared" ref="S2:S157" si="2">(O2/(M2+ N2 +O2))</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4"/>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>3</v>
+      </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
         <v>25</v>
@@ -1982,13 +2010,13 @@
         <v>26</v>
       </c>
       <c r="F3" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H3" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>22</v>
@@ -2003,30 +2031,32 @@
         <v>24</v>
       </c>
       <c r="M3" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N3" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R3" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S3" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4"/>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
         <v>28</v>
@@ -2038,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="F4" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G4" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H4" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>22</v>
@@ -2059,31 +2089,31 @@
         <v>24</v>
       </c>
       <c r="M4" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S4" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>196266.0</v>
+        <v>196266</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
@@ -2096,13 +2126,13 @@
         <v>32</v>
       </c>
       <c r="F5" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>22</v>
@@ -2117,30 +2147,32 @@
         <v>24</v>
       </c>
       <c r="M5" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R5" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4"/>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
         <v>34</v>
@@ -2152,13 +2184,13 @@
         <v>35</v>
       </c>
       <c r="F6" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H6" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>22</v>
@@ -2173,30 +2205,32 @@
         <v>24</v>
       </c>
       <c r="M6" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R6" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S6" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4"/>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
         <v>34</v>
@@ -2208,13 +2242,13 @@
         <v>37</v>
       </c>
       <c r="F7" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G7" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="3">
-        <v>2026.0</v>
+        <v>2026</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>22</v>
@@ -2229,31 +2263,31 @@
         <v>24</v>
       </c>
       <c r="M7" s="3">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="N7" s="3">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="O7" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="6">
-        <f t="shared" si="1"/>
-        <v>0.3253968254</v>
+        <f t="shared" si="0"/>
+        <v>0.32539682539682541</v>
       </c>
       <c r="R7" s="6">
-        <f t="shared" si="2"/>
-        <v>0.6746031746</v>
+        <f t="shared" si="1"/>
+        <v>0.67460317460317465</v>
       </c>
       <c r="S7" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>194982.0</v>
+        <v>194982</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>39</v>
@@ -2268,13 +2302,13 @@
         <v>42</v>
       </c>
       <c r="F8" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G8" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H8" s="3">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>22</v>
@@ -2289,31 +2323,31 @@
         <v>24</v>
       </c>
       <c r="M8" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R8" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>186947.0</v>
+        <v>186947</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>44</v>
@@ -2328,13 +2362,13 @@
         <v>46</v>
       </c>
       <c r="F9" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="G9" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H9" s="3">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>22</v>
@@ -2349,31 +2383,31 @@
         <v>24</v>
       </c>
       <c r="M9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P9" s="4"/>
-      <c r="Q9" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q9" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R9" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R9" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S9" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S9" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>186972.0</v>
+        <v>186972</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>48</v>
@@ -2388,13 +2422,13 @@
         <v>49</v>
       </c>
       <c r="F10" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H10" s="3">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>22</v>
@@ -2409,31 +2443,31 @@
         <v>24</v>
       </c>
       <c r="M10" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q10" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R10" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R10" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S10" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S10" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>186563.0</v>
+        <v>186563</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>51</v>
@@ -2448,13 +2482,13 @@
         <v>54</v>
       </c>
       <c r="F11" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G11" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>22</v>
@@ -2469,31 +2503,31 @@
         <v>24</v>
       </c>
       <c r="M11" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O11" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R11" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>190656.0</v>
+        <v>190656</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>56</v>
@@ -2508,13 +2542,13 @@
         <v>57</v>
       </c>
       <c r="F12" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="G12" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="3">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>22</v>
@@ -2529,31 +2563,31 @@
         <v>24</v>
       </c>
       <c r="M12" s="3">
-        <v>96.0</v>
+        <v>96</v>
       </c>
       <c r="N12" s="3">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="O12" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="6">
-        <f t="shared" si="1"/>
-        <v>0.6808510638</v>
+        <f t="shared" si="0"/>
+        <v>0.68085106382978722</v>
       </c>
       <c r="R12" s="6">
-        <f t="shared" si="2"/>
-        <v>0.3191489362</v>
+        <f t="shared" si="1"/>
+        <v>0.31914893617021278</v>
       </c>
       <c r="S12" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>172622.0</v>
+        <v>172622</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>59</v>
@@ -2568,13 +2602,13 @@
         <v>62</v>
       </c>
       <c r="F13" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H13" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>22</v>
@@ -2589,31 +2623,31 @@
         <v>24</v>
       </c>
       <c r="M13" s="3">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="N13" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="O13" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="6">
-        <f t="shared" si="1"/>
-        <v>0.8679245283</v>
+        <f t="shared" si="0"/>
+        <v>0.86792452830188682</v>
       </c>
       <c r="R13" s="6">
-        <f t="shared" si="2"/>
-        <v>0.1320754717</v>
+        <f t="shared" si="1"/>
+        <v>0.13207547169811321</v>
       </c>
       <c r="S13" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>184882.0</v>
+        <v>184882</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>64</v>
@@ -2628,13 +2662,13 @@
         <v>66</v>
       </c>
       <c r="F14" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G14" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H14" s="3">
-        <v>2017.0</v>
+        <v>2017</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>22</v>
@@ -2649,31 +2683,31 @@
         <v>24</v>
       </c>
       <c r="M14" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R14" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>191209.0</v>
+        <v>191209</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>68</v>
@@ -2688,13 +2722,13 @@
         <v>70</v>
       </c>
       <c r="F15" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>22</v>
@@ -2709,31 +2743,31 @@
         <v>24</v>
       </c>
       <c r="M15" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="O15" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R15" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S15" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>74542.0</v>
+        <v>74542</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>72</v>
@@ -2748,13 +2782,13 @@
         <v>75</v>
       </c>
       <c r="F16" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="G16" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="3">
-        <v>1988.0</v>
+        <v>1988</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>22</v>
@@ -2769,31 +2803,31 @@
         <v>24</v>
       </c>
       <c r="M16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3">
-        <v>209.0</v>
+        <v>209</v>
       </c>
       <c r="O16" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="6">
-        <f t="shared" si="1"/>
-        <v>0.004739336493</v>
+        <f t="shared" si="0"/>
+        <v>4.7393364928909956E-3</v>
       </c>
       <c r="R16" s="6">
-        <f t="shared" si="2"/>
-        <v>0.990521327</v>
+        <f t="shared" si="1"/>
+        <v>0.99052132701421802</v>
       </c>
       <c r="S16" s="6">
-        <f t="shared" si="3"/>
-        <v>0.004739336493</v>
-      </c>
-    </row>
-    <row r="17">
+        <f t="shared" si="2"/>
+        <v>4.7393364928909956E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>86350.0</v>
+        <v>86350</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>77</v>
@@ -2808,13 +2842,13 @@
         <v>79</v>
       </c>
       <c r="F17" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G17" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>22</v>
@@ -2829,29 +2863,29 @@
         <v>24</v>
       </c>
       <c r="M17" s="3">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="N17" s="3">
-        <v>54.0</v>
+        <v>54</v>
       </c>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="6">
-        <f t="shared" si="1"/>
-        <v>0.5263157895</v>
+        <f t="shared" si="0"/>
+        <v>0.52631578947368418</v>
       </c>
       <c r="R17" s="6">
-        <f t="shared" si="2"/>
-        <v>0.4736842105</v>
+        <f t="shared" si="1"/>
+        <v>0.47368421052631576</v>
       </c>
       <c r="S17" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>86366.0</v>
+        <v>86366</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>81</v>
@@ -2866,13 +2900,13 @@
         <v>82</v>
       </c>
       <c r="F18" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G18" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H18" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>22</v>
@@ -2887,31 +2921,31 @@
         <v>24</v>
       </c>
       <c r="M18" s="3">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="N18" s="3">
-        <v>74.0</v>
+        <v>74</v>
       </c>
       <c r="O18" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="6">
-        <f t="shared" si="1"/>
-        <v>0.393442623</v>
+        <f t="shared" si="0"/>
+        <v>0.39344262295081966</v>
       </c>
       <c r="R18" s="6">
-        <f t="shared" si="2"/>
-        <v>0.606557377</v>
+        <f t="shared" si="1"/>
+        <v>0.60655737704918034</v>
       </c>
       <c r="S18" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>13947.0</v>
+        <v>13947</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>84</v>
@@ -2926,13 +2960,13 @@
         <v>86</v>
       </c>
       <c r="F19" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H19" s="3">
-        <v>1970.0</v>
+        <v>1970</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>22</v>
@@ -2947,31 +2981,31 @@
         <v>24</v>
       </c>
       <c r="M19" s="3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="N19" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O19" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>86355.0</v>
+        <v>86355</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>88</v>
@@ -2986,13 +3020,13 @@
         <v>89</v>
       </c>
       <c r="F20" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H20" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>22</v>
@@ -3007,31 +3041,31 @@
         <v>24</v>
       </c>
       <c r="M20" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="N20" s="3">
-        <v>112.0</v>
+        <v>112</v>
       </c>
       <c r="O20" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1703703704</v>
+        <f t="shared" si="0"/>
+        <v>0.17037037037037037</v>
       </c>
       <c r="R20" s="6">
-        <f t="shared" si="2"/>
-        <v>0.8296296296</v>
+        <f t="shared" si="1"/>
+        <v>0.82962962962962961</v>
       </c>
       <c r="S20" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>189559.0</v>
+        <v>189559</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>91</v>
@@ -3046,13 +3080,13 @@
         <v>92</v>
       </c>
       <c r="F21" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G21" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H21" s="3">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>22</v>
@@ -3067,31 +3101,31 @@
         <v>24</v>
       </c>
       <c r="M21" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O21" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P21" s="4"/>
-      <c r="Q21" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q21" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R21" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R21" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S21" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S21" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>13950.0</v>
+        <v>13950</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>94</v>
@@ -3106,13 +3140,13 @@
         <v>86</v>
       </c>
       <c r="F22" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>22</v>
@@ -3127,31 +3161,31 @@
         <v>24</v>
       </c>
       <c r="M22" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R22" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>13951.0</v>
+        <v>13951</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>98</v>
@@ -3166,13 +3200,13 @@
         <v>86</v>
       </c>
       <c r="F23" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G23" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H23" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>22</v>
@@ -3187,31 +3221,31 @@
         <v>24</v>
       </c>
       <c r="M23" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
-        <v>155.0</v>
+        <v>155</v>
       </c>
       <c r="O23" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>65250.0</v>
+        <v>65250</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>99</v>
@@ -3226,13 +3260,13 @@
         <v>101</v>
       </c>
       <c r="F24" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="3">
-        <v>1987.0</v>
+        <v>1987</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>22</v>
@@ -3247,31 +3281,31 @@
         <v>24</v>
       </c>
       <c r="M24" s="3">
-        <v>108.0</v>
+        <v>108</v>
       </c>
       <c r="N24" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="O24" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P24" s="4"/>
       <c r="Q24" s="6">
-        <f t="shared" si="1"/>
-        <v>0.9310344828</v>
+        <f t="shared" si="0"/>
+        <v>0.93103448275862066</v>
       </c>
       <c r="R24" s="6">
-        <f t="shared" si="2"/>
-        <v>0.06896551724</v>
+        <f t="shared" si="1"/>
+        <v>6.8965517241379309E-2</v>
       </c>
       <c r="S24" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>142720.0</v>
+        <v>142720</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>103</v>
@@ -3286,13 +3320,13 @@
         <v>106</v>
       </c>
       <c r="F25" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G25" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H25" s="3">
-        <v>1998.0</v>
+        <v>1998</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>22</v>
@@ -3307,31 +3341,31 @@
         <v>24</v>
       </c>
       <c r="M25" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N25" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P25" s="4"/>
-      <c r="Q25" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q25" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R25" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R25" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S25" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>99518.0</v>
+        <v>99518</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>108</v>
@@ -3346,13 +3380,13 @@
         <v>110</v>
       </c>
       <c r="F26" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G26" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H26" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>22</v>
@@ -3367,31 +3401,31 @@
         <v>24</v>
       </c>
       <c r="M26" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P26" s="4"/>
       <c r="Q26" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R26" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S26" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>136087.0</v>
+        <v>136087</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>112</v>
@@ -3406,13 +3440,13 @@
         <v>114</v>
       </c>
       <c r="F27" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="3">
-        <v>1997.0</v>
+        <v>1997</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>22</v>
@@ -3427,31 +3461,31 @@
         <v>24</v>
       </c>
       <c r="M27" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="N27" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="O27" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P27" s="4"/>
       <c r="Q27" s="6">
-        <f t="shared" si="1"/>
-        <v>0.425</v>
+        <f t="shared" si="0"/>
+        <v>0.42499999999999999</v>
       </c>
       <c r="R27" s="6">
-        <f t="shared" si="2"/>
-        <v>0.575</v>
+        <f t="shared" si="1"/>
+        <v>0.57499999999999996</v>
       </c>
       <c r="S27" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>135771.0</v>
+        <v>135771</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>116</v>
@@ -3466,13 +3500,13 @@
         <v>117</v>
       </c>
       <c r="F28" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G28" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H28" s="3">
-        <v>1997.0</v>
+        <v>1997</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>22</v>
@@ -3487,31 +3521,31 @@
         <v>24</v>
       </c>
       <c r="M28" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N28" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="O28" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P28" s="4"/>
       <c r="Q28" s="6">
-        <f t="shared" si="1"/>
-        <v>0.2083333333</v>
+        <f t="shared" si="0"/>
+        <v>0.20833333333333334</v>
       </c>
       <c r="R28" s="6">
-        <f t="shared" si="2"/>
-        <v>0.7916666667</v>
+        <f t="shared" si="1"/>
+        <v>0.79166666666666663</v>
       </c>
       <c r="S28" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>154147.0</v>
+        <v>154147</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>119</v>
@@ -3526,13 +3560,13 @@
         <v>120</v>
       </c>
       <c r="F29" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="G29" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H29" s="3">
-        <v>2001.0</v>
+        <v>2001</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>22</v>
@@ -3547,31 +3581,31 @@
         <v>24</v>
       </c>
       <c r="M29" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N29" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P29" s="4"/>
       <c r="Q29" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R29" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S29" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>159877.0</v>
+        <v>159877</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>122</v>
@@ -3586,13 +3620,13 @@
         <v>125</v>
       </c>
       <c r="F30" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3">
-        <v>2006.0</v>
+        <v>2006</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>22</v>
@@ -3607,31 +3641,31 @@
         <v>24</v>
       </c>
       <c r="M30" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N30" s="3">
-        <v>213.0</v>
+        <v>213</v>
       </c>
       <c r="O30" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P30" s="4"/>
       <c r="Q30" s="6">
-        <f t="shared" si="1"/>
-        <v>0.01843317972</v>
+        <f t="shared" si="0"/>
+        <v>1.8433179723502304E-2</v>
       </c>
       <c r="R30" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9815668203</v>
+        <f t="shared" si="1"/>
+        <v>0.98156682027649766</v>
       </c>
       <c r="S30" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>168248.0</v>
+        <v>168248</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>127</v>
@@ -3646,13 +3680,13 @@
         <v>129</v>
       </c>
       <c r="F31" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H31" s="3">
-        <v>2009.0</v>
+        <v>2009</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>22</v>
@@ -3667,31 +3701,31 @@
         <v>24</v>
       </c>
       <c r="M31" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N31" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="O31" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
       <c r="R31" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.88</v>
       </c>
       <c r="S31" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>172694.0</v>
+        <v>172694</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>131</v>
@@ -3706,13 +3740,13 @@
         <v>134</v>
       </c>
       <c r="F32" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G32" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H32" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>22</v>
@@ -3727,31 +3761,31 @@
         <v>24</v>
       </c>
       <c r="M32" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="O32" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P32" s="4"/>
       <c r="Q32" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R32" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S32" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>182600.0</v>
+        <v>182600</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>136</v>
@@ -3766,13 +3800,13 @@
         <v>138</v>
       </c>
       <c r="F33" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H33" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>22</v>
@@ -3787,31 +3821,31 @@
         <v>24</v>
       </c>
       <c r="M33" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="3">
-        <v>110.0</v>
+        <v>110</v>
       </c>
       <c r="O33" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P33" s="4"/>
       <c r="Q33" s="6">
-        <f t="shared" si="1"/>
-        <v>0.009009009009</v>
+        <f t="shared" si="0"/>
+        <v>9.0090090090090089E-3</v>
       </c>
       <c r="R33" s="6">
-        <f t="shared" si="2"/>
-        <v>0.990990991</v>
+        <f t="shared" si="1"/>
+        <v>0.99099099099099097</v>
       </c>
       <c r="S33" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>173564.0</v>
+        <v>173564</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>140</v>
@@ -3826,13 +3860,13 @@
         <v>142</v>
       </c>
       <c r="F34" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G34" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H34" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>22</v>
@@ -3847,31 +3881,31 @@
         <v>24</v>
       </c>
       <c r="M34" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="3">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="O34" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P34" s="4"/>
       <c r="Q34" s="6">
-        <f t="shared" si="1"/>
-        <v>0.01162790698</v>
+        <f t="shared" si="0"/>
+        <v>1.1627906976744186E-2</v>
       </c>
       <c r="R34" s="6">
-        <f t="shared" si="2"/>
-        <v>0.988372093</v>
+        <f t="shared" si="1"/>
+        <v>0.98837209302325579</v>
       </c>
       <c r="S34" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>13942.0</v>
+        <v>13942</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>143</v>
@@ -3886,13 +3920,13 @@
         <v>86</v>
       </c>
       <c r="F35" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G35" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H35" s="3">
-        <v>1939.0</v>
+        <v>1939</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>22</v>
@@ -3905,31 +3939,31 @@
         <v>24</v>
       </c>
       <c r="M35" s="3">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="N35" s="3">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P35" s="4"/>
       <c r="Q35" s="6">
-        <f t="shared" si="1"/>
-        <v>0.2805755396</v>
+        <f t="shared" si="0"/>
+        <v>0.2805755395683453</v>
       </c>
       <c r="R35" s="6">
-        <f t="shared" si="2"/>
-        <v>0.7194244604</v>
+        <f t="shared" si="1"/>
+        <v>0.71942446043165464</v>
       </c>
       <c r="S35" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>13944.0</v>
+        <v>13944</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>146</v>
@@ -3941,16 +3975,16 @@
         <v>147</v>
       </c>
       <c r="E36" s="3">
-        <v>808.0</v>
+        <v>808</v>
       </c>
       <c r="F36" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="G36" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H36" s="3">
-        <v>1970.0</v>
+        <v>1970</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>22</v>
@@ -3965,31 +3999,31 @@
         <v>24</v>
       </c>
       <c r="M36" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N36" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P36" s="4"/>
       <c r="Q36" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R36" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S36" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>13946.0</v>
+        <v>13946</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>149</v>
@@ -4004,13 +4038,13 @@
         <v>86</v>
       </c>
       <c r="F37" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G37" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H37" s="3">
-        <v>1937.0</v>
+        <v>1937</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>22</v>
@@ -4023,31 +4057,31 @@
         <v>24</v>
       </c>
       <c r="M37" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N37" s="3">
-        <v>56.0</v>
+        <v>56</v>
       </c>
       <c r="O37" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P37" s="4"/>
       <c r="Q37" s="6">
-        <f t="shared" si="1"/>
-        <v>0.03448275862</v>
+        <f t="shared" si="0"/>
+        <v>3.4482758620689655E-2</v>
       </c>
       <c r="R37" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9655172414</v>
+        <f t="shared" si="1"/>
+        <v>0.96551724137931039</v>
       </c>
       <c r="S37" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>13945.0</v>
+        <v>13945</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>150</v>
@@ -4062,13 +4096,13 @@
         <v>86</v>
       </c>
       <c r="F38" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G38" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H38" s="3">
-        <v>1970.0</v>
+        <v>1970</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>22</v>
@@ -4083,31 +4117,31 @@
         <v>24</v>
       </c>
       <c r="M38" s="3">
-        <v>275.0</v>
+        <v>275</v>
       </c>
       <c r="N38" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P38" s="4"/>
       <c r="Q38" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R38" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S38" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>131836.0</v>
+        <v>131836</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>152</v>
@@ -4122,13 +4156,13 @@
         <v>154</v>
       </c>
       <c r="F39" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G39" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H39" s="3">
-        <v>1996.0</v>
+        <v>1996</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>22</v>
@@ -4143,31 +4177,31 @@
         <v>24</v>
       </c>
       <c r="M39" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N39" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="O39" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P39" s="4"/>
       <c r="Q39" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R39" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S39" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>92588.0</v>
+        <v>92588</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>156</v>
@@ -4182,13 +4216,13 @@
         <v>157</v>
       </c>
       <c r="F40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G40" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H40" s="3">
-        <v>1990.0</v>
+        <v>1990</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>22</v>
@@ -4203,31 +4237,31 @@
         <v>24</v>
       </c>
       <c r="M40" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N40" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O40" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P40" s="4"/>
       <c r="Q40" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R40" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S40" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
-        <v>35454.0</v>
+        <v>35454</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>159</v>
@@ -4242,13 +4276,13 @@
         <v>86</v>
       </c>
       <c r="F41" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G41" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3">
-        <v>1977.0</v>
+        <v>1977</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>22</v>
@@ -4263,31 +4297,31 @@
         <v>24</v>
       </c>
       <c r="M41" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N41" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P41" s="4"/>
-      <c r="Q41" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q41" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R41" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R41" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S41" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S41" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
-        <v>75004.0</v>
+        <v>75004</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>162</v>
@@ -4302,13 +4336,13 @@
         <v>163</v>
       </c>
       <c r="F42" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="G42" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H42" s="3">
-        <v>1988.0</v>
+        <v>1988</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>22</v>
@@ -4323,31 +4357,31 @@
         <v>24</v>
       </c>
       <c r="M42" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N42" s="3">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="O42" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P42" s="4"/>
       <c r="Q42" s="6">
-        <f t="shared" si="1"/>
-        <v>0.08510638298</v>
+        <f t="shared" si="0"/>
+        <v>8.5106382978723402E-2</v>
       </c>
       <c r="R42" s="6">
-        <f t="shared" si="2"/>
-        <v>0.914893617</v>
+        <f t="shared" si="1"/>
+        <v>0.91489361702127658</v>
       </c>
       <c r="S42" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>182535.0</v>
+        <v>182535</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>164</v>
@@ -4362,13 +4396,13 @@
         <v>166</v>
       </c>
       <c r="F43" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H43" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>22</v>
@@ -4383,31 +4417,31 @@
         <v>24</v>
       </c>
       <c r="M43" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
-        <v>115.0</v>
+        <v>115</v>
       </c>
       <c r="O43" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P43" s="4"/>
       <c r="Q43" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R43" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S43" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>13915.0</v>
+        <v>13915</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>168</v>
@@ -4422,13 +4456,13 @@
         <v>86</v>
       </c>
       <c r="F44" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G44" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H44" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>22</v>
@@ -4443,31 +4477,31 @@
         <v>24</v>
       </c>
       <c r="M44" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N44" s="3">
-        <v>142.0</v>
+        <v>142</v>
       </c>
       <c r="O44" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P44" s="4"/>
       <c r="Q44" s="6">
-        <f t="shared" si="1"/>
-        <v>0.01388888889</v>
+        <f t="shared" si="0"/>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="R44" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9861111111</v>
+        <f t="shared" si="1"/>
+        <v>0.98611111111111116</v>
       </c>
       <c r="S44" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <v>126779.0</v>
+        <v>126779</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>170</v>
@@ -4482,13 +4516,13 @@
         <v>171</v>
       </c>
       <c r="F45" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G45" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H45" s="3">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>22</v>
@@ -4503,31 +4537,31 @@
         <v>24</v>
       </c>
       <c r="M45" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N45" s="3">
-        <v>92.0</v>
+        <v>92</v>
       </c>
       <c r="O45" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P45" s="4"/>
       <c r="Q45" s="6">
-        <f t="shared" si="1"/>
-        <v>0.05154639175</v>
+        <f t="shared" si="0"/>
+        <v>5.1546391752577317E-2</v>
       </c>
       <c r="R45" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9484536082</v>
+        <f t="shared" si="1"/>
+        <v>0.94845360824742264</v>
       </c>
       <c r="S45" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <v>86735.0</v>
+        <v>86735</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>173</v>
@@ -4542,13 +4576,13 @@
         <v>175</v>
       </c>
       <c r="F46" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="G46" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H46" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>22</v>
@@ -4563,31 +4597,31 @@
         <v>24</v>
       </c>
       <c r="M46" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="3">
-        <v>103.0</v>
+        <v>103</v>
       </c>
       <c r="O46" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P46" s="4"/>
       <c r="Q46" s="6">
-        <f t="shared" si="1"/>
-        <v>0.009615384615</v>
+        <f t="shared" si="0"/>
+        <v>9.6153846153846159E-3</v>
       </c>
       <c r="R46" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9903846154</v>
+        <f t="shared" si="1"/>
+        <v>0.99038461538461542</v>
       </c>
       <c r="S46" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>111803.0</v>
+        <v>111803</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>177</v>
@@ -4602,13 +4636,13 @@
         <v>179</v>
       </c>
       <c r="F47" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G47" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H47" s="3">
-        <v>1993.0</v>
+        <v>1993</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>22</v>
@@ -4623,31 +4657,31 @@
         <v>24</v>
       </c>
       <c r="M47" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="O47" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P47" s="4"/>
       <c r="Q47" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R47" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S47" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <v>126740.0</v>
+        <v>126740</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>181</v>
@@ -4662,13 +4696,13 @@
         <v>182</v>
       </c>
       <c r="F48" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G48" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H48" s="3">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>22</v>
@@ -4683,31 +4717,31 @@
         <v>24</v>
       </c>
       <c r="M48" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N48" s="3">
-        <v>53.0</v>
+        <v>53</v>
       </c>
       <c r="O48" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P48" s="4"/>
       <c r="Q48" s="6">
-        <f t="shared" si="1"/>
-        <v>0.131147541</v>
+        <f t="shared" si="0"/>
+        <v>0.13114754098360656</v>
       </c>
       <c r="R48" s="6">
-        <f t="shared" si="2"/>
-        <v>0.868852459</v>
+        <f t="shared" si="1"/>
+        <v>0.86885245901639341</v>
       </c>
       <c r="S48" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <v>85641.0</v>
+        <v>85641</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>184</v>
@@ -4722,13 +4756,13 @@
         <v>185</v>
       </c>
       <c r="F49" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G49" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H49" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>22</v>
@@ -4743,31 +4777,31 @@
         <v>24</v>
       </c>
       <c r="M49" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N49" s="3">
-        <v>158.0</v>
+        <v>158</v>
       </c>
       <c r="O49" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P49" s="4"/>
       <c r="Q49" s="6">
-        <f t="shared" si="1"/>
-        <v>0.05952380952</v>
+        <f t="shared" si="0"/>
+        <v>5.9523809523809521E-2</v>
       </c>
       <c r="R49" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9404761905</v>
+        <f t="shared" si="1"/>
+        <v>0.94047619047619047</v>
       </c>
       <c r="S49" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <v>182597.0</v>
+        <v>182597</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>187</v>
@@ -4782,13 +4816,13 @@
         <v>188</v>
       </c>
       <c r="F50" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G50" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H50" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>22</v>
@@ -4803,31 +4837,31 @@
         <v>24</v>
       </c>
       <c r="M50" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N50" s="3">
-        <v>146.0</v>
+        <v>146</v>
       </c>
       <c r="O50" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P50" s="4"/>
       <c r="Q50" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R50" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S50" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <v>167146.0</v>
+        <v>167146</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>190</v>
@@ -4842,13 +4876,13 @@
         <v>191</v>
       </c>
       <c r="F51" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G51" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H51" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>22</v>
@@ -4863,31 +4897,31 @@
         <v>24</v>
       </c>
       <c r="M51" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N51" s="3">
-        <v>64.0</v>
+        <v>64</v>
       </c>
       <c r="O51" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P51" s="4"/>
       <c r="Q51" s="6">
-        <f t="shared" si="1"/>
-        <v>0.07246376812</v>
+        <f t="shared" si="0"/>
+        <v>7.2463768115942032E-2</v>
       </c>
       <c r="R51" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9275362319</v>
+        <f t="shared" si="1"/>
+        <v>0.92753623188405798</v>
       </c>
       <c r="S51" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
-        <v>184229.0</v>
+        <v>184229</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>193</v>
@@ -4902,13 +4936,13 @@
         <v>194</v>
       </c>
       <c r="F52" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G52" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3">
-        <v>2017.0</v>
+        <v>2017</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>22</v>
@@ -4923,31 +4957,31 @@
         <v>24</v>
       </c>
       <c r="M52" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
-        <v>129.0</v>
+        <v>129</v>
       </c>
       <c r="O52" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P52" s="4"/>
       <c r="Q52" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R52" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S52" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
-        <v>171143.0</v>
+        <v>171143</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>196</v>
@@ -4962,13 +4996,13 @@
         <v>198</v>
       </c>
       <c r="F53" s="3">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="G53" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H53" s="3">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>22</v>
@@ -4983,31 +5017,31 @@
         <v>24</v>
       </c>
       <c r="M53" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N53" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="O53" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P53" s="4"/>
       <c r="Q53" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R53" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S53" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
-        <v>170320.0</v>
+        <v>170320</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>200</v>
@@ -5022,13 +5056,13 @@
         <v>201</v>
       </c>
       <c r="F54" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G54" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H54" s="3">
-        <v>2009.0</v>
+        <v>2009</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>22</v>
@@ -5043,31 +5077,31 @@
         <v>24</v>
       </c>
       <c r="M54" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="N54" s="3">
-        <v>154.0</v>
+        <v>154</v>
       </c>
       <c r="O54" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P54" s="4"/>
       <c r="Q54" s="6">
-        <f t="shared" si="1"/>
-        <v>0.09941520468</v>
+        <f t="shared" si="0"/>
+        <v>9.9415204678362568E-2</v>
       </c>
       <c r="R54" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9005847953</v>
+        <f t="shared" si="1"/>
+        <v>0.90058479532163738</v>
       </c>
       <c r="S54" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
-        <v>160615.0</v>
+        <v>160615</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>203</v>
@@ -5082,13 +5116,13 @@
         <v>205</v>
       </c>
       <c r="F55" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G55" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="3">
-        <v>2006.0</v>
+        <v>2006</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>22</v>
@@ -5103,31 +5137,31 @@
         <v>24</v>
       </c>
       <c r="M55" s="3">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="N55" s="3">
-        <v>144.0</v>
+        <v>144</v>
       </c>
       <c r="O55" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P55" s="4"/>
       <c r="Q55" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1578947368</v>
+        <f t="shared" si="0"/>
+        <v>0.15789473684210525</v>
       </c>
       <c r="R55" s="6">
-        <f t="shared" si="2"/>
-        <v>0.8421052632</v>
+        <f t="shared" si="1"/>
+        <v>0.84210526315789469</v>
       </c>
       <c r="S55" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
-        <v>135721.0</v>
+        <v>135721</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>207</v>
@@ -5142,13 +5176,13 @@
         <v>209</v>
       </c>
       <c r="F56" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="G56" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H56" s="3">
-        <v>1997.0</v>
+        <v>1997</v>
       </c>
       <c r="I56" s="4" t="s">
         <v>22</v>
@@ -5163,31 +5197,31 @@
         <v>24</v>
       </c>
       <c r="M56" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N56" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="O56" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P56" s="4"/>
       <c r="Q56" s="6">
-        <f t="shared" si="1"/>
-        <v>0.4666666667</v>
+        <f t="shared" si="0"/>
+        <v>0.46666666666666667</v>
       </c>
       <c r="R56" s="6">
-        <f t="shared" si="2"/>
-        <v>0.5333333333</v>
+        <f t="shared" si="1"/>
+        <v>0.53333333333333333</v>
       </c>
       <c r="S56" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
-        <v>182537.0</v>
+        <v>182537</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>211</v>
@@ -5202,13 +5236,13 @@
         <v>212</v>
       </c>
       <c r="F57" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G57" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H57" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>22</v>
@@ -5223,31 +5257,31 @@
         <v>24</v>
       </c>
       <c r="M57" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N57" s="3">
-        <v>201.0</v>
+        <v>201</v>
       </c>
       <c r="O57" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P57" s="4"/>
       <c r="Q57" s="6">
-        <f t="shared" si="1"/>
-        <v>0.01470588235</v>
+        <f t="shared" si="0"/>
+        <v>1.4705882352941176E-2</v>
       </c>
       <c r="R57" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9852941176</v>
+        <f t="shared" si="1"/>
+        <v>0.98529411764705888</v>
       </c>
       <c r="S57" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
-        <v>186689.0</v>
+        <v>186689</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>214</v>
@@ -5262,13 +5296,13 @@
         <v>215</v>
       </c>
       <c r="F58" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="G58" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="3">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>22</v>
@@ -5283,31 +5317,31 @@
         <v>24</v>
       </c>
       <c r="M58" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="3">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="O58" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P58" s="4"/>
       <c r="Q58" s="6">
-        <f t="shared" si="1"/>
-        <v>0.01785714286</v>
+        <f t="shared" si="0"/>
+        <v>1.7857142857142856E-2</v>
       </c>
       <c r="R58" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9821428571</v>
+        <f t="shared" si="1"/>
+        <v>0.9821428571428571</v>
       </c>
       <c r="S58" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
-        <v>172935.0</v>
+        <v>172935</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>217</v>
@@ -5322,13 +5356,13 @@
         <v>218</v>
       </c>
       <c r="F59" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G59" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>22</v>
@@ -5343,31 +5377,31 @@
         <v>24</v>
       </c>
       <c r="M59" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="N59" s="3">
-        <v>121.0</v>
+        <v>121</v>
       </c>
       <c r="O59" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P59" s="4"/>
       <c r="Q59" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1538461538</v>
+        <f t="shared" si="0"/>
+        <v>0.15384615384615385</v>
       </c>
       <c r="R59" s="6">
-        <f t="shared" si="2"/>
-        <v>0.8461538462</v>
+        <f t="shared" si="1"/>
+        <v>0.84615384615384615</v>
       </c>
       <c r="S59" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
-        <v>91528.0</v>
+        <v>91528</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>220</v>
@@ -5382,13 +5416,13 @@
         <v>222</v>
       </c>
       <c r="F60" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G60" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H60" s="3">
-        <v>1990.0</v>
+        <v>1990</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>22</v>
@@ -5403,31 +5437,31 @@
         <v>24</v>
       </c>
       <c r="M60" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
-        <v>68.0</v>
+        <v>68</v>
       </c>
       <c r="O60" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P60" s="4"/>
       <c r="Q60" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R60" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S60" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
-        <v>182536.0</v>
+        <v>182536</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>224</v>
@@ -5442,13 +5476,13 @@
         <v>225</v>
       </c>
       <c r="F61" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G61" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>22</v>
@@ -5463,31 +5497,31 @@
         <v>24</v>
       </c>
       <c r="M61" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>153.0</v>
+        <v>153</v>
       </c>
       <c r="O61" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P61" s="4"/>
       <c r="Q61" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R61" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S61" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
-        <v>182533.0</v>
+        <v>182533</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>227</v>
@@ -5502,13 +5536,13 @@
         <v>228</v>
       </c>
       <c r="F62" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H62" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>22</v>
@@ -5523,31 +5557,31 @@
         <v>24</v>
       </c>
       <c r="M62" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N62" s="3">
-        <v>109.0</v>
+        <v>109</v>
       </c>
       <c r="O62" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P62" s="4"/>
       <c r="Q62" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R62" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S62" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
-        <v>167017.0</v>
+        <v>167017</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>230</v>
@@ -5562,13 +5596,13 @@
         <v>231</v>
       </c>
       <c r="F63" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G63" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>22</v>
@@ -5583,31 +5617,31 @@
         <v>24</v>
       </c>
       <c r="M63" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N63" s="3">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="O63" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P63" s="4"/>
       <c r="Q63" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R63" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S63" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
-        <v>182596.0</v>
+        <v>182596</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>233</v>
@@ -5622,13 +5656,13 @@
         <v>235</v>
       </c>
       <c r="F64" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>22</v>
@@ -5643,31 +5677,31 @@
         <v>24</v>
       </c>
       <c r="M64" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="N64" s="3">
-        <v>118.0</v>
+        <v>118</v>
       </c>
       <c r="O64" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P64" s="4"/>
       <c r="Q64" s="6">
-        <f t="shared" si="1"/>
-        <v>0.1510791367</v>
+        <f t="shared" si="0"/>
+        <v>0.15107913669064749</v>
       </c>
       <c r="R64" s="6">
-        <f t="shared" si="2"/>
-        <v>0.8489208633</v>
+        <f t="shared" si="1"/>
+        <v>0.84892086330935257</v>
       </c>
       <c r="S64" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
-        <v>159987.0</v>
+        <v>159987</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>237</v>
@@ -5682,13 +5716,13 @@
         <v>239</v>
       </c>
       <c r="F65" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H65" s="3">
-        <v>2006.0</v>
+        <v>2006</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>22</v>
@@ -5703,31 +5737,31 @@
         <v>24</v>
       </c>
       <c r="M65" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N65" s="3">
-        <v>136.0</v>
+        <v>136</v>
       </c>
       <c r="O65" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P65" s="4"/>
       <c r="Q65" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R65" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S65" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
-        <v>167027.0</v>
+        <v>167027</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>241</v>
@@ -5742,13 +5776,13 @@
         <v>242</v>
       </c>
       <c r="F66" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G66" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>22</v>
@@ -5763,31 +5797,31 @@
         <v>24</v>
       </c>
       <c r="M66" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3">
-        <v>104.0</v>
+        <v>104</v>
       </c>
       <c r="O66" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P66" s="4"/>
       <c r="Q66" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R66" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S66" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
-        <v>171283.0</v>
+        <v>171283</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>244</v>
@@ -5802,13 +5836,13 @@
         <v>245</v>
       </c>
       <c r="F67" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G67" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="3">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>22</v>
@@ -5823,31 +5857,31 @@
         <v>24</v>
       </c>
       <c r="M67" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N67" s="3">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="O67" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P67" s="4"/>
       <c r="Q67" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R67" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S67" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
-        <v>182531.0</v>
+        <v>182531</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>247</v>
@@ -5862,13 +5896,13 @@
         <v>248</v>
       </c>
       <c r="F68" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G68" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H68" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>22</v>
@@ -5883,31 +5917,31 @@
         <v>24</v>
       </c>
       <c r="M68" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="N68" s="3">
-        <v>191.0</v>
+        <v>191</v>
       </c>
       <c r="O68" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P68" s="4"/>
       <c r="Q68" s="6">
-        <f t="shared" si="1"/>
-        <v>0.0103626943</v>
+        <f t="shared" si="0"/>
+        <v>1.0362694300518135E-2</v>
       </c>
       <c r="R68" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9896373057</v>
+        <f t="shared" si="1"/>
+        <v>0.98963730569948183</v>
       </c>
       <c r="S68" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
-        <v>182598.0</v>
+        <v>182598</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>250</v>
@@ -5922,13 +5956,13 @@
         <v>251</v>
       </c>
       <c r="F69" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G69" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H69" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>22</v>
@@ -5943,31 +5977,31 @@
         <v>24</v>
       </c>
       <c r="M69" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N69" s="3">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="O69" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P69" s="4"/>
       <c r="Q69" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R69" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S69" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
-        <v>131430.0</v>
+        <v>131430</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>253</v>
@@ -5982,13 +6016,13 @@
         <v>254</v>
       </c>
       <c r="F70" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G70" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H70" s="3">
-        <v>1996.0</v>
+        <v>1996</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>22</v>
@@ -6003,31 +6037,31 @@
         <v>24</v>
       </c>
       <c r="M70" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O70" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P70" s="4"/>
       <c r="Q70" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R70" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S70" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
-        <v>126741.0</v>
+        <v>126741</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>256</v>
@@ -6042,13 +6076,13 @@
         <v>257</v>
       </c>
       <c r="F71" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G71" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H71" s="3">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>22</v>
@@ -6063,31 +6097,31 @@
         <v>24</v>
       </c>
       <c r="M71" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N71" s="3">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="O71" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P71" s="4"/>
       <c r="Q71" s="6">
-        <f t="shared" si="1"/>
-        <v>0.02127659574</v>
+        <f t="shared" si="0"/>
+        <v>2.1276595744680851E-2</v>
       </c>
       <c r="R71" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9787234043</v>
+        <f t="shared" si="1"/>
+        <v>0.97872340425531912</v>
       </c>
       <c r="S71" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
-        <v>131629.0</v>
+        <v>131629</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>259</v>
@@ -6102,13 +6136,13 @@
         <v>261</v>
       </c>
       <c r="F72" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G72" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H72" s="3">
-        <v>1996.0</v>
+        <v>1996</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>22</v>
@@ -6123,31 +6157,31 @@
         <v>24</v>
       </c>
       <c r="M72" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N72" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="O72" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P72" s="4"/>
       <c r="Q72" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R72" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S72" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
-        <v>182635.0</v>
+        <v>182635</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>263</v>
@@ -6162,13 +6196,13 @@
         <v>264</v>
       </c>
       <c r="F73" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H73" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>22</v>
@@ -6183,31 +6217,31 @@
         <v>24</v>
       </c>
       <c r="M73" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N73" s="3">
-        <v>194.0</v>
+        <v>194</v>
       </c>
       <c r="O73" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P73" s="4"/>
       <c r="Q73" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R73" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S73" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
-        <v>182534.0</v>
+        <v>182534</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>266</v>
@@ -6222,13 +6256,13 @@
         <v>267</v>
       </c>
       <c r="F74" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G74" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H74" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>22</v>
@@ -6243,31 +6277,31 @@
         <v>24</v>
       </c>
       <c r="M74" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="N74" s="3">
-        <v>192.0</v>
+        <v>192</v>
       </c>
       <c r="O74" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P74" s="4"/>
       <c r="Q74" s="6">
-        <f t="shared" si="1"/>
-        <v>0.02040816327</v>
+        <f t="shared" si="0"/>
+        <v>2.0408163265306121E-2</v>
       </c>
       <c r="R74" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9795918367</v>
+        <f t="shared" si="1"/>
+        <v>0.97959183673469385</v>
       </c>
       <c r="S74" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
-        <v>131518.0</v>
+        <v>131518</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>269</v>
@@ -6282,13 +6316,13 @@
         <v>270</v>
       </c>
       <c r="F75" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G75" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H75" s="3">
-        <v>1996.0</v>
+        <v>1996</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>22</v>
@@ -6303,31 +6337,31 @@
         <v>24</v>
       </c>
       <c r="M75" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="N75" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="O75" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P75" s="4"/>
       <c r="Q75" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.3125</v>
       </c>
       <c r="R75" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.6875</v>
       </c>
       <c r="S75" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
-        <v>182532.0</v>
+        <v>182532</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>272</v>
@@ -6342,13 +6376,13 @@
         <v>273</v>
       </c>
       <c r="F76" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G76" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H76" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>22</v>
@@ -6363,31 +6397,31 @@
         <v>24</v>
       </c>
       <c r="M76" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="3">
-        <v>178.0</v>
+        <v>178</v>
       </c>
       <c r="O76" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P76" s="4"/>
       <c r="Q76" s="6">
-        <f t="shared" si="1"/>
-        <v>0.005586592179</v>
+        <f t="shared" si="0"/>
+        <v>5.5865921787709499E-3</v>
       </c>
       <c r="R76" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9944134078</v>
+        <f t="shared" si="1"/>
+        <v>0.994413407821229</v>
       </c>
       <c r="S76" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
-        <v>167258.0</v>
+        <v>167258</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>275</v>
@@ -6402,13 +6436,13 @@
         <v>276</v>
       </c>
       <c r="F77" s="3">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="G77" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H77" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>22</v>
@@ -6423,31 +6457,31 @@
         <v>24</v>
       </c>
       <c r="M77" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N77" s="3">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="O77" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P77" s="4"/>
       <c r="Q77" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R77" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S77" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
-        <v>104064.0</v>
+        <v>104064</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>278</v>
@@ -6462,13 +6496,13 @@
         <v>279</v>
       </c>
       <c r="F78" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G78" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H78" s="3">
-        <v>1992.0</v>
+        <v>1992</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>22</v>
@@ -6483,31 +6517,31 @@
         <v>24</v>
       </c>
       <c r="M78" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N78" s="3">
-        <v>195.0</v>
+        <v>195</v>
       </c>
       <c r="O78" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P78" s="4"/>
       <c r="Q78" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R78" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S78" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
-        <v>126780.0</v>
+        <v>126780</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>281</v>
@@ -6522,13 +6556,13 @@
         <v>282</v>
       </c>
       <c r="F79" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G79" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H79" s="3">
-        <v>1995.0</v>
+        <v>1995</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>22</v>
@@ -6543,31 +6577,31 @@
         <v>24</v>
       </c>
       <c r="M79" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N79" s="3">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="O79" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P79" s="4"/>
       <c r="Q79" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R79" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S79" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
-        <v>172613.0</v>
+        <v>172613</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>284</v>
@@ -6582,13 +6616,13 @@
         <v>285</v>
       </c>
       <c r="F80" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G80" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H80" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>22</v>
@@ -6603,31 +6637,31 @@
         <v>24</v>
       </c>
       <c r="M80" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N80" s="3">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="O80" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P80" s="4"/>
       <c r="Q80" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R80" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S80" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
-        <v>182599.0</v>
+        <v>182599</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>287</v>
@@ -6642,13 +6676,13 @@
         <v>288</v>
       </c>
       <c r="F81" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G81" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H81" s="3">
-        <v>2016.0</v>
+        <v>2016</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>22</v>
@@ -6663,31 +6697,31 @@
         <v>24</v>
       </c>
       <c r="M81" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N81" s="3">
-        <v>190.0</v>
+        <v>190</v>
       </c>
       <c r="O81" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P81" s="4"/>
       <c r="Q81" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
       <c r="R81" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="S81" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
-        <v>131370.0</v>
+        <v>131370</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>290</v>
@@ -6702,13 +6736,13 @@
         <v>291</v>
       </c>
       <c r="F82" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G82" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3">
-        <v>1996.0</v>
+        <v>1996</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>22</v>
@@ -6723,31 +6757,31 @@
         <v>24</v>
       </c>
       <c r="M82" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N82" s="3">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="O82" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P82" s="4"/>
       <c r="Q82" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R82" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S82" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
-        <v>173922.0</v>
+        <v>173922</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>293</v>
@@ -6762,13 +6796,13 @@
         <v>294</v>
       </c>
       <c r="F83" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="G83" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H83" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>22</v>
@@ -6783,29 +6817,29 @@
         <v>24</v>
       </c>
       <c r="M83" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
-        <v>123.0</v>
+        <v>123</v>
       </c>
       <c r="O83" s="4"/>
       <c r="P83" s="4"/>
       <c r="Q83" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R83" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S83" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
-        <v>186568.0</v>
+        <v>186568</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>296</v>
@@ -6820,13 +6854,13 @@
         <v>297</v>
       </c>
       <c r="F84" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G84" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H84" s="3">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>22</v>
@@ -6841,31 +6875,31 @@
         <v>24</v>
       </c>
       <c r="M84" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N84" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O84" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P84" s="4"/>
       <c r="Q84" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R84" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S84" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
-        <v>186866.0</v>
+        <v>186866</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>299</v>
@@ -6880,13 +6914,13 @@
         <v>300</v>
       </c>
       <c r="F85" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="G85" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H85" s="3">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>22</v>
@@ -6901,31 +6935,31 @@
         <v>24</v>
       </c>
       <c r="M85" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N85" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P85" s="4"/>
       <c r="Q85" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R85" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S85" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
-        <v>187274.0</v>
+        <v>187274</v>
       </c>
       <c r="B86" s="4" t="s">
         <v>302</v>
@@ -6940,13 +6974,13 @@
         <v>303</v>
       </c>
       <c r="F86" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G86" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H86" s="3">
-        <v>2019.0</v>
+        <v>2019</v>
       </c>
       <c r="I86" s="4" t="s">
         <v>22</v>
@@ -6961,31 +6995,31 @@
         <v>24</v>
       </c>
       <c r="M86" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N86" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O86" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P86" s="4"/>
       <c r="Q86" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R86" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S86" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
-        <v>182175.0</v>
+        <v>182175</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>305</v>
@@ -7000,13 +7034,13 @@
         <v>306</v>
       </c>
       <c r="F87" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="G87" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H87" s="3">
-        <v>2015.0</v>
+        <v>2015</v>
       </c>
       <c r="I87" s="4" t="s">
         <v>22</v>
@@ -7021,31 +7055,31 @@
         <v>24</v>
       </c>
       <c r="M87" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N87" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O87" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P87" s="4"/>
       <c r="Q87" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R87" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S87" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
-        <v>188363.0</v>
+        <v>188363</v>
       </c>
       <c r="B88" s="4" t="s">
         <v>308</v>
@@ -7060,13 +7094,13 @@
         <v>309</v>
       </c>
       <c r="F88" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="G88" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H88" s="3">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>22</v>
@@ -7081,31 +7115,31 @@
         <v>24</v>
       </c>
       <c r="M88" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N88" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O88" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P88" s="4"/>
       <c r="Q88" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R88" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S88" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
-        <v>188392.0</v>
+        <v>188392</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>311</v>
@@ -7120,13 +7154,13 @@
         <v>312</v>
       </c>
       <c r="F89" s="3">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="G89" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H89" s="3">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="I89" s="4" t="s">
         <v>22</v>
@@ -7141,31 +7175,31 @@
         <v>24</v>
       </c>
       <c r="M89" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P89" s="4"/>
       <c r="Q89" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R89" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S89" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
-        <v>190657.0</v>
+        <v>190657</v>
       </c>
       <c r="B90" s="4" t="s">
         <v>314</v>
@@ -7180,13 +7214,13 @@
         <v>315</v>
       </c>
       <c r="F90" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="G90" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H90" s="3">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>22</v>
@@ -7201,31 +7235,31 @@
         <v>24</v>
       </c>
       <c r="M90" s="3">
-        <v>141.0</v>
+        <v>141</v>
       </c>
       <c r="N90" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="O90" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P90" s="4"/>
       <c r="Q90" s="6">
-        <f t="shared" si="1"/>
-        <v>0.8924050633</v>
+        <f t="shared" si="0"/>
+        <v>0.89240506329113922</v>
       </c>
       <c r="R90" s="6">
-        <f t="shared" si="2"/>
-        <v>0.1075949367</v>
+        <f t="shared" si="1"/>
+        <v>0.10759493670886076</v>
       </c>
       <c r="S90" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
-        <v>188398.0</v>
+        <v>188398</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>317</v>
@@ -7240,13 +7274,13 @@
         <v>318</v>
       </c>
       <c r="F91" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G91" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H91" s="3">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>22</v>
@@ -7261,31 +7295,31 @@
         <v>24</v>
       </c>
       <c r="M91" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P91" s="4"/>
       <c r="Q91" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R91" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S91" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
-        <v>190846.0</v>
+        <v>190846</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>320</v>
@@ -7300,13 +7334,13 @@
         <v>321</v>
       </c>
       <c r="F92" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G92" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H92" s="3">
-        <v>2023.0</v>
+        <v>2023</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>22</v>
@@ -7321,31 +7355,31 @@
         <v>24</v>
       </c>
       <c r="M92" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N92" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O92" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P92" s="4"/>
       <c r="Q92" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R92" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S92" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
-        <v>194022.0</v>
+        <v>194022</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>323</v>
@@ -7360,13 +7394,13 @@
         <v>324</v>
       </c>
       <c r="F93" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G93" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="H93" s="3">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>22</v>
@@ -7381,31 +7415,31 @@
         <v>24</v>
       </c>
       <c r="M93" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N93" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O93" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="P93" s="4"/>
       <c r="Q93" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R93" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S93" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
-        <v>167139.0</v>
+        <v>167139</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>326</v>
@@ -7420,13 +7454,13 @@
         <v>328</v>
       </c>
       <c r="F94" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G94" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H94" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>22</v>
@@ -7441,31 +7475,31 @@
         <v>24</v>
       </c>
       <c r="M94" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P94" s="4"/>
       <c r="Q94" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R94" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S94" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
-        <v>104979.0</v>
+        <v>104979</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>329</v>
@@ -7480,13 +7514,13 @@
         <v>331</v>
       </c>
       <c r="F95" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G95" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H95" s="3">
-        <v>1992.0</v>
+        <v>1992</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>22</v>
@@ -7501,31 +7535,31 @@
         <v>24</v>
       </c>
       <c r="M95" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N95" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O95" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P95" s="4"/>
       <c r="Q95" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R95" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S95" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
-        <v>98146.0</v>
+        <v>98146</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>333</v>
@@ -7540,13 +7574,13 @@
         <v>86</v>
       </c>
       <c r="F96" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G96" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H96" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>22</v>
@@ -7561,31 +7595,31 @@
         <v>24</v>
       </c>
       <c r="M96" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P96" s="4"/>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q96" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R96" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R96" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S96" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S96" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
-        <v>185097.0</v>
+        <v>185097</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>336</v>
@@ -7600,13 +7634,13 @@
         <v>338</v>
       </c>
       <c r="F97" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G97" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H97" s="3">
-        <v>2017.0</v>
+        <v>2017</v>
       </c>
       <c r="I97" s="4" t="s">
         <v>22</v>
@@ -7621,31 +7655,31 @@
         <v>24</v>
       </c>
       <c r="M97" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N97" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O97" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P97" s="4"/>
-      <c r="Q97" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q97" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R97" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R97" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S97" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S97" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
-        <v>177026.0</v>
+        <v>177026</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>339</v>
@@ -7660,13 +7694,13 @@
         <v>341</v>
       </c>
       <c r="F98" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H98" s="3">
-        <v>2013.0</v>
+        <v>2013</v>
       </c>
       <c r="I98" s="4" t="s">
         <v>22</v>
@@ -7681,31 +7715,31 @@
         <v>24</v>
       </c>
       <c r="M98" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N98" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O98" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="P98" s="4"/>
       <c r="Q98" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R98" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S98" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
-        <v>174551.0</v>
+        <v>174551</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>343</v>
@@ -7720,13 +7754,13 @@
         <v>344</v>
       </c>
       <c r="F99" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G99" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H99" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I99" s="4" t="s">
         <v>22</v>
@@ -7741,31 +7775,31 @@
         <v>24</v>
       </c>
       <c r="M99" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N99" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O99" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="P99" s="4"/>
       <c r="Q99" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R99" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S99" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
-        <v>167137.0</v>
+        <v>167137</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>345</v>
@@ -7780,13 +7814,13 @@
         <v>346</v>
       </c>
       <c r="F100" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G100" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H100" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>22</v>
@@ -7801,31 +7835,31 @@
         <v>24</v>
       </c>
       <c r="M100" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N100" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="4"/>
       <c r="Q100" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R100" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S100" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
-        <v>95904.0</v>
+        <v>95904</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>348</v>
@@ -7840,13 +7874,13 @@
         <v>349</v>
       </c>
       <c r="F101" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G101" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H101" s="3">
-        <v>1990.0</v>
+        <v>1990</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>22</v>
@@ -7861,31 +7895,31 @@
         <v>24</v>
       </c>
       <c r="M101" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P101" s="4"/>
       <c r="Q101" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R101" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S101" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
-        <v>175477.0</v>
+        <v>175477</v>
       </c>
       <c r="B102" s="4" t="s">
         <v>351</v>
@@ -7900,13 +7934,13 @@
         <v>352</v>
       </c>
       <c r="F102" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G102" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H102" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>22</v>
@@ -7921,31 +7955,31 @@
         <v>24</v>
       </c>
       <c r="M102" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P102" s="4"/>
       <c r="Q102" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R102" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S102" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
-        <v>159654.0</v>
+        <v>159654</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>354</v>
@@ -7960,13 +7994,13 @@
         <v>356</v>
       </c>
       <c r="F103" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G103" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H103" s="3">
-        <v>2005.0</v>
+        <v>2005</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>22</v>
@@ -7981,31 +8015,31 @@
         <v>24</v>
       </c>
       <c r="M103" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N103" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O103" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P103" s="4"/>
       <c r="Q103" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R103" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S103" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
-        <v>13914.0</v>
+        <v>13914</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>358</v>
@@ -8020,13 +8054,13 @@
         <v>86</v>
       </c>
       <c r="F104" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G104" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H104" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>22</v>
@@ -8041,31 +8075,31 @@
         <v>24</v>
       </c>
       <c r="M104" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N104" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O104" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P104" s="4"/>
-      <c r="Q104" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q104" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R104" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R104" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S104" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S104" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
-        <v>175310.0</v>
+        <v>175310</v>
       </c>
       <c r="B105" s="4" t="s">
         <v>360</v>
@@ -8080,13 +8114,13 @@
         <v>361</v>
       </c>
       <c r="F105" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G105" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H105" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>22</v>
@@ -8101,31 +8135,31 @@
         <v>24</v>
       </c>
       <c r="M105" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N105" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O105" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P105" s="4"/>
       <c r="Q105" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R105" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S105" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
-        <v>172712.0</v>
+        <v>172712</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>363</v>
@@ -8140,13 +8174,13 @@
         <v>365</v>
       </c>
       <c r="F106" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G106" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H106" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I106" s="4" t="s">
         <v>22</v>
@@ -8161,31 +8195,31 @@
         <v>24</v>
       </c>
       <c r="M106" s="3">
-        <v>119.0</v>
+        <v>119</v>
       </c>
       <c r="N106" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="O106" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P106" s="4"/>
       <c r="Q106" s="6">
-        <f t="shared" si="1"/>
-        <v>0.8321678322</v>
+        <f t="shared" si="0"/>
+        <v>0.83216783216783219</v>
       </c>
       <c r="R106" s="6">
-        <f t="shared" si="2"/>
-        <v>0.1678321678</v>
+        <f t="shared" si="1"/>
+        <v>0.16783216783216784</v>
       </c>
       <c r="S106" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
-        <v>175442.0</v>
+        <v>175442</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>367</v>
@@ -8200,13 +8234,13 @@
         <v>369</v>
       </c>
       <c r="F107" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G107" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H107" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>22</v>
@@ -8221,31 +8255,31 @@
         <v>24</v>
       </c>
       <c r="M107" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N107" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O107" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P107" s="4"/>
       <c r="Q107" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R107" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S107" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
-        <v>96308.0</v>
+        <v>96308</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>371</v>
@@ -8260,13 +8294,13 @@
         <v>372</v>
       </c>
       <c r="F108" s="3">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="G108" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H108" s="3">
-        <v>1990.0</v>
+        <v>1990</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>22</v>
@@ -8281,31 +8315,31 @@
         <v>24</v>
       </c>
       <c r="M108" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N108" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O108" s="3">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="P108" s="4"/>
       <c r="Q108" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R108" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S108" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
-        <v>168377.0</v>
+        <v>168377</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>374</v>
@@ -8320,13 +8354,13 @@
         <v>376</v>
       </c>
       <c r="F109" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G109" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H109" s="3">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="I109" s="4" t="s">
         <v>22</v>
@@ -8341,31 +8375,31 @@
         <v>24</v>
       </c>
       <c r="M109" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N109" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O109" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P109" s="4"/>
       <c r="Q109" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R109" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S109" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
-        <v>80381.0</v>
+        <v>80381</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>378</v>
@@ -8380,13 +8414,13 @@
         <v>380</v>
       </c>
       <c r="F110" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G110" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H110" s="3">
-        <v>1988.0</v>
+        <v>1988</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>22</v>
@@ -8401,31 +8435,31 @@
         <v>24</v>
       </c>
       <c r="M110" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N110" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O110" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P110" s="4"/>
       <c r="Q110" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R110" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S110" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
-        <v>172617.0</v>
+        <v>172617</v>
       </c>
       <c r="B111" s="4" t="s">
         <v>381</v>
@@ -8440,13 +8474,13 @@
         <v>382</v>
       </c>
       <c r="F111" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G111" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H111" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>22</v>
@@ -8461,31 +8495,31 @@
         <v>24</v>
       </c>
       <c r="M111" s="3">
-        <v>82.0</v>
+        <v>82</v>
       </c>
       <c r="N111" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="O111" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P111" s="4"/>
       <c r="Q111" s="6">
-        <f t="shared" si="1"/>
-        <v>0.9647058824</v>
+        <f t="shared" si="0"/>
+        <v>0.96470588235294119</v>
       </c>
       <c r="R111" s="6">
-        <f t="shared" si="2"/>
-        <v>0.03529411765</v>
+        <f t="shared" si="1"/>
+        <v>3.5294117647058823E-2</v>
       </c>
       <c r="S111" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
-        <v>164172.0</v>
+        <v>164172</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>384</v>
@@ -8500,13 +8534,13 @@
         <v>385</v>
       </c>
       <c r="F112" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G112" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H112" s="3">
-        <v>2007.0</v>
+        <v>2007</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>22</v>
@@ -8521,31 +8555,31 @@
         <v>24</v>
       </c>
       <c r="M112" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N112" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O112" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P112" s="4"/>
       <c r="Q112" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R112" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S112" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>13919.0</v>
+        <v>13919</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>387</v>
@@ -8560,13 +8594,13 @@
         <v>86</v>
       </c>
       <c r="F113" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G113" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H113" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>22</v>
@@ -8581,31 +8615,31 @@
         <v>24</v>
       </c>
       <c r="M113" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N113" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O113" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="P113" s="4"/>
       <c r="Q113" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R113" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S113" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>151859.0</v>
+        <v>151859</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>389</v>
@@ -8620,13 +8654,13 @@
         <v>390</v>
       </c>
       <c r="F114" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="G114" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H114" s="3">
-        <v>2001.0</v>
+        <v>2001</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>22</v>
@@ -8641,31 +8675,31 @@
         <v>24</v>
       </c>
       <c r="M114" s="3">
-        <v>137.0</v>
+        <v>137</v>
       </c>
       <c r="N114" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O114" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P114" s="4"/>
       <c r="Q114" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R114" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S114" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>171378.0</v>
+        <v>171378</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>392</v>
@@ -8680,13 +8714,13 @@
         <v>393</v>
       </c>
       <c r="F115" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G115" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H115" s="3">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>22</v>
@@ -8701,31 +8735,31 @@
         <v>24</v>
       </c>
       <c r="M115" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N115" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O115" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P115" s="4"/>
       <c r="Q115" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R115" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S115" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
-        <v>174552.0</v>
+        <v>174552</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>395</v>
@@ -8740,13 +8774,13 @@
         <v>396</v>
       </c>
       <c r="F116" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G116" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H116" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>22</v>
@@ -8761,31 +8795,31 @@
         <v>24</v>
       </c>
       <c r="M116" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N116" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O116" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P116" s="4"/>
       <c r="Q116" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R116" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S116" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
-        <v>172325.0</v>
+        <v>172325</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>397</v>
@@ -8800,13 +8834,13 @@
         <v>398</v>
       </c>
       <c r="F117" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G117" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H117" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>22</v>
@@ -8821,31 +8855,31 @@
         <v>24</v>
       </c>
       <c r="M117" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N117" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O117" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P117" s="4"/>
       <c r="Q117" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R117" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S117" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
-        <v>172327.0</v>
+        <v>172327</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>400</v>
@@ -8860,13 +8894,13 @@
         <v>401</v>
       </c>
       <c r="F118" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G118" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H118" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>22</v>
@@ -8881,31 +8915,31 @@
         <v>24</v>
       </c>
       <c r="M118" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N118" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O118" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P118" s="4"/>
       <c r="Q118" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R118" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S118" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
-        <v>169880.0</v>
+        <v>169880</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>403</v>
@@ -8920,13 +8954,13 @@
         <v>405</v>
       </c>
       <c r="F119" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G119" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H119" s="3">
-        <v>2009.0</v>
+        <v>2009</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>22</v>
@@ -8941,31 +8975,31 @@
         <v>24</v>
       </c>
       <c r="M119" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N119" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O119" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P119" s="4"/>
       <c r="Q119" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R119" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S119" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
-        <v>97408.0</v>
+        <v>97408</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>406</v>
@@ -8980,13 +9014,13 @@
         <v>407</v>
       </c>
       <c r="F120" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G120" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H120" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>22</v>
@@ -9001,31 +9035,31 @@
         <v>24</v>
       </c>
       <c r="M120" s="3">
-        <v>228.0</v>
+        <v>228</v>
       </c>
       <c r="N120" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O120" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P120" s="4"/>
       <c r="Q120" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R120" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S120" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
-        <v>172326.0</v>
+        <v>172326</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>409</v>
@@ -9040,13 +9074,13 @@
         <v>410</v>
       </c>
       <c r="F121" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G121" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H121" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>22</v>
@@ -9061,31 +9095,31 @@
         <v>24</v>
       </c>
       <c r="M121" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N121" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O121" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P121" s="4"/>
       <c r="Q121" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R121" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S121" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
-        <v>13916.0</v>
+        <v>13916</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>412</v>
@@ -9100,13 +9134,13 @@
         <v>86</v>
       </c>
       <c r="F122" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G122" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H122" s="3">
-        <v>1937.0</v>
+        <v>1937</v>
       </c>
       <c r="I122" s="4" t="s">
         <v>22</v>
@@ -9121,31 +9155,31 @@
         <v>24</v>
       </c>
       <c r="M122" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N122" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O122" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P122" s="4"/>
-      <c r="Q122" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q122" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R122" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R122" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S122" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S122" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
-        <v>104989.0</v>
+        <v>104989</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>414</v>
@@ -9160,13 +9194,13 @@
         <v>415</v>
       </c>
       <c r="F123" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G123" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H123" s="3">
-        <v>1992.0</v>
+        <v>1992</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>22</v>
@@ -9181,31 +9215,31 @@
         <v>24</v>
       </c>
       <c r="M123" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N123" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O123" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="P123" s="4"/>
       <c r="Q123" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R123" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S123" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
-        <v>151871.0</v>
+        <v>151871</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>417</v>
@@ -9220,13 +9254,13 @@
         <v>418</v>
       </c>
       <c r="F124" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="G124" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H124" s="3">
-        <v>2001.0</v>
+        <v>2001</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>22</v>
@@ -9241,31 +9275,31 @@
         <v>24</v>
       </c>
       <c r="M124" s="3">
-        <v>135.0</v>
+        <v>135</v>
       </c>
       <c r="N124" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O124" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P124" s="4"/>
       <c r="Q124" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R124" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S124" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
-        <v>151924.0</v>
+        <v>151924</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>420</v>
@@ -9280,13 +9314,13 @@
         <v>421</v>
       </c>
       <c r="F125" s="3">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="G125" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H125" s="3">
-        <v>2001.0</v>
+        <v>2001</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>22</v>
@@ -9301,31 +9335,31 @@
         <v>24</v>
       </c>
       <c r="M125" s="3">
-        <v>59.0</v>
+        <v>59</v>
       </c>
       <c r="N125" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O125" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P125" s="4"/>
       <c r="Q125" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R125" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S125" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>13918.0</v>
+        <v>13918</v>
       </c>
       <c r="B126" s="4" t="s">
         <v>423</v>
@@ -9340,13 +9374,13 @@
         <v>86</v>
       </c>
       <c r="F126" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G126" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H126" s="3">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>22</v>
@@ -9370,22 +9404,22 @@
       <c r="P126" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="Q126" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q126" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="R126" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R126" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="S126" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S126" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>175213.0</v>
+        <v>175213</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>427</v>
@@ -9400,13 +9434,13 @@
         <v>428</v>
       </c>
       <c r="F127" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G127" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H127" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>22</v>
@@ -9421,31 +9455,31 @@
         <v>24</v>
       </c>
       <c r="M127" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N127" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O127" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P127" s="4"/>
       <c r="Q127" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R127" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S127" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>164652.0</v>
+        <v>164652</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>430</v>
@@ -9460,13 +9494,13 @@
         <v>431</v>
       </c>
       <c r="F128" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G128" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H128" s="3">
-        <v>2007.0</v>
+        <v>2007</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>22</v>
@@ -9481,31 +9515,31 @@
         <v>24</v>
       </c>
       <c r="M128" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N128" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O128" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="P128" s="4"/>
       <c r="Q128" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R128" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S128" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
-        <v>184867.0</v>
+        <v>184867</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>433</v>
@@ -9520,13 +9554,13 @@
         <v>434</v>
       </c>
       <c r="F129" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="G129" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H129" s="3">
-        <v>2017.0</v>
+        <v>2017</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>22</v>
@@ -9541,31 +9575,31 @@
         <v>24</v>
       </c>
       <c r="M129" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N129" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O129" s="3">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="P129" s="4"/>
       <c r="Q129" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R129" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S129" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
-        <v>175492.0</v>
+        <v>175492</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>436</v>
@@ -9580,13 +9614,13 @@
         <v>437</v>
       </c>
       <c r="F130" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G130" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H130" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>22</v>
@@ -9601,31 +9635,31 @@
         <v>24</v>
       </c>
       <c r="M130" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N130" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O130" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P130" s="4"/>
       <c r="Q130" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R130" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S130" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
-        <v>184285.0</v>
+        <v>184285</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>439</v>
@@ -9640,13 +9674,13 @@
         <v>440</v>
       </c>
       <c r="F131" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G131" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H131" s="3">
-        <v>2017.0</v>
+        <v>2017</v>
       </c>
       <c r="I131" s="4" t="s">
         <v>22</v>
@@ -9661,31 +9695,31 @@
         <v>24</v>
       </c>
       <c r="M131" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N131" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O131" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P131" s="4"/>
       <c r="Q131" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R131" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S131" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
-        <v>164333.0</v>
+        <v>164333</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>442</v>
@@ -9700,13 +9734,13 @@
         <v>443</v>
       </c>
       <c r="F132" s="3">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="G132" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H132" s="3">
-        <v>2007.0</v>
+        <v>2007</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>22</v>
@@ -9721,31 +9755,31 @@
         <v>24</v>
       </c>
       <c r="M132" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N132" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O132" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P132" s="4"/>
       <c r="Q132" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R132" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S132" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
-        <v>97238.0</v>
+        <v>97238</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>445</v>
@@ -9760,13 +9794,13 @@
         <v>446</v>
       </c>
       <c r="F133" s="3">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="G133" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H133" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I133" s="4" t="s">
         <v>22</v>
@@ -9781,31 +9815,31 @@
         <v>24</v>
       </c>
       <c r="M133" s="3">
-        <v>305.0</v>
+        <v>305</v>
       </c>
       <c r="N133" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O133" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P133" s="4"/>
       <c r="Q133" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R133" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S133" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>177778.0</v>
+        <v>177778</v>
       </c>
       <c r="B134" s="4" t="s">
         <v>448</v>
@@ -9820,13 +9854,13 @@
         <v>450</v>
       </c>
       <c r="F134" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G134" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H134" s="3">
-        <v>2012.0</v>
+        <v>2012</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>22</v>
@@ -9841,31 +9875,31 @@
         <v>24</v>
       </c>
       <c r="M134" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N134" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O134" s="3">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P134" s="4"/>
       <c r="Q134" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R134" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S134" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
-        <v>168362.0</v>
+        <v>168362</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>452</v>
@@ -9880,13 +9914,13 @@
         <v>454</v>
       </c>
       <c r="F135" s="3">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="G135" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H135" s="3">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>22</v>
@@ -9901,31 +9935,31 @@
         <v>24</v>
       </c>
       <c r="M135" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N135" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O135" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P135" s="4"/>
       <c r="Q135" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R135" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S135" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
-        <v>177027.0</v>
+        <v>177027</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>456</v>
@@ -9940,13 +9974,13 @@
         <v>457</v>
       </c>
       <c r="F136" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H136" s="3">
-        <v>2013.0</v>
+        <v>2013</v>
       </c>
       <c r="I136" s="4" t="s">
         <v>22</v>
@@ -9961,31 +9995,31 @@
         <v>24</v>
       </c>
       <c r="M136" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N136" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O136" s="3">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="P136" s="4"/>
       <c r="Q136" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R136" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S136" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
-        <v>85786.0</v>
+        <v>85786</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>459</v>
@@ -10000,13 +10034,13 @@
         <v>460</v>
       </c>
       <c r="F137" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G137" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H137" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I137" s="4" t="s">
         <v>22</v>
@@ -10021,29 +10055,29 @@
         <v>24</v>
       </c>
       <c r="M137" s="3">
-        <v>85.0</v>
+        <v>85</v>
       </c>
       <c r="N137" s="3">
-        <v>72.0</v>
+        <v>72</v>
       </c>
       <c r="O137" s="4"/>
       <c r="P137" s="4"/>
       <c r="Q137" s="6">
-        <f t="shared" si="1"/>
-        <v>0.5414012739</v>
+        <f t="shared" si="0"/>
+        <v>0.54140127388535031</v>
       </c>
       <c r="R137" s="6">
-        <f t="shared" si="2"/>
-        <v>0.4585987261</v>
+        <f t="shared" si="1"/>
+        <v>0.45859872611464969</v>
       </c>
       <c r="S137" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
-        <v>97248.0</v>
+        <v>97248</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>462</v>
@@ -10058,13 +10092,13 @@
         <v>463</v>
       </c>
       <c r="F138" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G138" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H138" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I138" s="4" t="s">
         <v>22</v>
@@ -10079,31 +10113,31 @@
         <v>24</v>
       </c>
       <c r="M138" s="3">
-        <v>134.0</v>
+        <v>134</v>
       </c>
       <c r="N138" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O138" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P138" s="4"/>
       <c r="Q138" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R138" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S138" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
-        <v>172560.0</v>
+        <v>172560</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>464</v>
@@ -10118,13 +10152,13 @@
         <v>465</v>
       </c>
       <c r="F139" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G139" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H139" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I139" s="4" t="s">
         <v>22</v>
@@ -10139,31 +10173,31 @@
         <v>24</v>
       </c>
       <c r="M139" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N139" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O139" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P139" s="4"/>
       <c r="Q139" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R139" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S139" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
-        <v>167720.0</v>
+        <v>167720</v>
       </c>
       <c r="B140" s="4" t="s">
         <v>467</v>
@@ -10178,13 +10212,13 @@
         <v>468</v>
       </c>
       <c r="F140" s="3">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="G140" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H140" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I140" s="4" t="s">
         <v>22</v>
@@ -10199,31 +10233,31 @@
         <v>24</v>
       </c>
       <c r="M140" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N140" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O140" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P140" s="4"/>
       <c r="Q140" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R140" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S140" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
-        <v>98711.0</v>
+        <v>98711</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>470</v>
@@ -10238,13 +10272,13 @@
         <v>471</v>
       </c>
       <c r="F141" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G141" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="H141" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>22</v>
@@ -10259,31 +10293,31 @@
         <v>24</v>
       </c>
       <c r="M141" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N141" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O141" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="P141" s="4"/>
       <c r="Q141" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R141" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S141" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
-        <v>159918.0</v>
+        <v>159918</v>
       </c>
       <c r="B142" s="4" t="s">
         <v>472</v>
@@ -10298,13 +10332,13 @@
         <v>474</v>
       </c>
       <c r="F142" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G142" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H142" s="3">
-        <v>2006.0</v>
+        <v>2006</v>
       </c>
       <c r="I142" s="4" t="s">
         <v>22</v>
@@ -10319,31 +10353,31 @@
         <v>24</v>
       </c>
       <c r="M142" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N142" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O142" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P142" s="4"/>
       <c r="Q142" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R142" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S142" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
-        <v>166555.0</v>
+        <v>166555</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>476</v>
@@ -10358,13 +10392,13 @@
         <v>477</v>
       </c>
       <c r="F143" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G143" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H143" s="3">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="I143" s="4" t="s">
         <v>22</v>
@@ -10379,31 +10413,31 @@
         <v>24</v>
       </c>
       <c r="M143" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="N143" s="3">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="O143" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P143" s="4"/>
       <c r="Q143" s="6">
-        <f t="shared" si="1"/>
-        <v>0.3333333333</v>
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R143" s="6">
-        <f t="shared" si="2"/>
-        <v>0.6666666667</v>
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="S143" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
-        <v>172713.0</v>
+        <v>172713</v>
       </c>
       <c r="B144" s="4" t="s">
         <v>479</v>
@@ -10418,13 +10452,13 @@
         <v>480</v>
       </c>
       <c r="F144" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G144" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H144" s="3">
-        <v>2011.0</v>
+        <v>2011</v>
       </c>
       <c r="I144" s="4" t="s">
         <v>22</v>
@@ -10439,31 +10473,31 @@
         <v>24</v>
       </c>
       <c r="M144" s="3">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="N144" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="O144" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P144" s="4"/>
       <c r="Q144" s="6">
-        <f t="shared" si="1"/>
-        <v>0.8706896552</v>
+        <f t="shared" si="0"/>
+        <v>0.87068965517241381</v>
       </c>
       <c r="R144" s="6">
-        <f t="shared" si="2"/>
-        <v>0.1293103448</v>
+        <f t="shared" si="1"/>
+        <v>0.12931034482758622</v>
       </c>
       <c r="S144" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
-        <v>85800.0</v>
+        <v>85800</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>482</v>
@@ -10478,13 +10512,13 @@
         <v>483</v>
       </c>
       <c r="F145" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G145" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H145" s="3">
-        <v>1989.0</v>
+        <v>1989</v>
       </c>
       <c r="I145" s="4" t="s">
         <v>22</v>
@@ -10499,31 +10533,31 @@
         <v>24</v>
       </c>
       <c r="M145" s="3">
-        <v>121.0</v>
+        <v>121</v>
       </c>
       <c r="N145" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="O145" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P145" s="4"/>
       <c r="Q145" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.9453125</v>
       </c>
       <c r="R145" s="6">
-        <f t="shared" si="2"/>
-        <v>0.0546875</v>
+        <f t="shared" si="1"/>
+        <v>5.46875E-2</v>
       </c>
       <c r="S145" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
-        <v>75322.0</v>
+        <v>75322</v>
       </c>
       <c r="B146" s="4" t="s">
         <v>485</v>
@@ -10538,13 +10572,13 @@
         <v>486</v>
       </c>
       <c r="F146" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G146" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H146" s="3">
-        <v>1987.0</v>
+        <v>1987</v>
       </c>
       <c r="I146" s="4" t="s">
         <v>22</v>
@@ -10559,31 +10593,31 @@
         <v>24</v>
       </c>
       <c r="M146" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N146" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O146" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="P146" s="4"/>
       <c r="Q146" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R146" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S146" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
-        <v>13954.0</v>
+        <v>13954</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>488</v>
@@ -10598,13 +10632,13 @@
         <v>86</v>
       </c>
       <c r="F147" s="3">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="G147" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H147" s="3">
-        <v>1923.0</v>
+        <v>1923</v>
       </c>
       <c r="I147" s="4" t="s">
         <v>22</v>
@@ -10617,33 +10651,33 @@
         <v>24</v>
       </c>
       <c r="M147" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N147" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O147" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P147" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="Q147" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q147" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R147" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R147" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S147" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S147" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
-        <v>113047.0</v>
+        <v>113047</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>491</v>
@@ -10658,13 +10692,13 @@
         <v>492</v>
       </c>
       <c r="F148" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G148" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H148" s="3">
-        <v>1993.0</v>
+        <v>1993</v>
       </c>
       <c r="I148" s="4" t="s">
         <v>22</v>
@@ -10679,31 +10713,31 @@
         <v>24</v>
       </c>
       <c r="M148" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N148" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O148" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="P148" s="4"/>
       <c r="Q148" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R148" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S148" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
-        <v>75870.0</v>
+        <v>75870</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>494</v>
@@ -10718,13 +10752,13 @@
         <v>495</v>
       </c>
       <c r="F149" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G149" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H149" s="3">
-        <v>1987.0</v>
+        <v>1987</v>
       </c>
       <c r="I149" s="4" t="s">
         <v>22</v>
@@ -10739,31 +10773,31 @@
         <v>24</v>
       </c>
       <c r="M149" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N149" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O149" s="3">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="P149" s="4"/>
       <c r="Q149" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R149" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S149" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
-        <v>13952.0</v>
+        <v>13952</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>497</v>
@@ -10778,13 +10812,13 @@
         <v>86</v>
       </c>
       <c r="F150" s="3">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G150" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H150" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I150" s="4" t="s">
         <v>22</v>
@@ -10799,31 +10833,31 @@
         <v>24</v>
       </c>
       <c r="M150" s="3">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="N150" s="3">
-        <v>98.0</v>
+        <v>98</v>
       </c>
       <c r="O150" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P150" s="4"/>
       <c r="Q150" s="6">
-        <f t="shared" si="1"/>
-        <v>0.0297029703</v>
+        <f t="shared" si="0"/>
+        <v>2.9702970297029702E-2</v>
       </c>
       <c r="R150" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9702970297</v>
+        <f t="shared" si="1"/>
+        <v>0.97029702970297027</v>
       </c>
       <c r="S150" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
-        <v>97411.0</v>
+        <v>97411</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>499</v>
@@ -10838,13 +10872,13 @@
         <v>500</v>
       </c>
       <c r="F151" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="G151" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H151" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I151" s="4" t="s">
         <v>22</v>
@@ -10859,31 +10893,31 @@
         <v>24</v>
       </c>
       <c r="M151" s="3">
-        <v>165.0</v>
+        <v>165</v>
       </c>
       <c r="N151" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O151" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P151" s="4"/>
       <c r="Q151" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="R151" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S151" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
-        <v>113773.0</v>
+        <v>113773</v>
       </c>
       <c r="B152" s="4" t="s">
         <v>502</v>
@@ -10898,13 +10932,13 @@
         <v>503</v>
       </c>
       <c r="F152" s="3">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="G152" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H152" s="3">
-        <v>1993.0</v>
+        <v>1993</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>22</v>
@@ -10919,31 +10953,31 @@
         <v>24</v>
       </c>
       <c r="M152" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N152" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O152" s="3">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="P152" s="4"/>
       <c r="Q152" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R152" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S152" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
-        <v>97931.0</v>
+        <v>97931</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>505</v>
@@ -10958,13 +10992,13 @@
         <v>506</v>
       </c>
       <c r="F153" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="G153" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H153" s="3">
-        <v>1991.0</v>
+        <v>1991</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>22</v>
@@ -10979,31 +11013,31 @@
         <v>24</v>
       </c>
       <c r="M153" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N153" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="O153" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P153" s="4"/>
       <c r="Q153" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R153" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S153" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
-        <v>112989.0</v>
+        <v>112989</v>
       </c>
       <c r="B154" s="4" t="s">
         <v>508</v>
@@ -11018,13 +11052,13 @@
         <v>509</v>
       </c>
       <c r="F154" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G154" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H154" s="3">
-        <v>1993.0</v>
+        <v>1993</v>
       </c>
       <c r="I154" s="4" t="s">
         <v>22</v>
@@ -11039,31 +11073,31 @@
         <v>24</v>
       </c>
       <c r="M154" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N154" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O154" s="3">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="P154" s="4"/>
       <c r="Q154" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R154" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S154" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
-        <v>13953.0</v>
+        <v>13953</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>510</v>
@@ -11078,13 +11112,13 @@
         <v>86</v>
       </c>
       <c r="F155" s="3">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="G155" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H155" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>22</v>
@@ -11099,31 +11133,31 @@
         <v>24</v>
       </c>
       <c r="M155" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N155" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O155" s="3">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="P155" s="4"/>
       <c r="Q155" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R155" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S155" s="6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
-        <v>13959.0</v>
+        <v>13959</v>
       </c>
       <c r="B156" s="4" t="s">
         <v>511</v>
@@ -11138,13 +11172,13 @@
         <v>86</v>
       </c>
       <c r="F156" s="3">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G156" s="3">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="H156" s="3">
-        <v>1975.0</v>
+        <v>1975</v>
       </c>
       <c r="I156" s="4" t="s">
         <v>22</v>
@@ -11159,31 +11193,31 @@
         <v>24</v>
       </c>
       <c r="M156" s="3">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="N156" s="3">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="O156" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P156" s="4"/>
       <c r="Q156" s="6">
-        <f t="shared" si="1"/>
-        <v>0.09090909091</v>
+        <f t="shared" si="0"/>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="R156" s="6">
-        <f t="shared" si="2"/>
-        <v>0.9090909091</v>
+        <f t="shared" si="1"/>
+        <v>0.90909090909090906</v>
       </c>
       <c r="S156" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
-        <v>13960.0</v>
+        <v>13960</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>515</v>
@@ -11198,13 +11232,13 @@
         <v>86</v>
       </c>
       <c r="F157" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G157" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="H157" s="3">
-        <v>1971.0</v>
+        <v>1971</v>
       </c>
       <c r="I157" s="4" t="s">
         <v>22</v>
@@ -11219,34 +11253,34 @@
         <v>24</v>
       </c>
       <c r="M157" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="N157" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="O157" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="P157" s="4"/>
-      <c r="Q157" s="6" t="str">
-        <f t="shared" si="1"/>
+      <c r="Q157" s="6" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R157" s="6" t="str">
-        <f t="shared" si="2"/>
+      <c r="R157" s="6" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S157" s="6" t="str">
-        <f t="shared" si="3"/>
+      <c r="S157" s="6" t="e">
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L157">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L2:L157" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>